--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-media-endoscopy.xlsx
@@ -835,7 +835,7 @@
     <t>このメディアを生成した装置名。</t>
   </si>
   <si>
-    <t>原則機種名（スコープ）を記載する。デジカメの場合Exifヘッダの機種名とする。</t>
+    <t>原則機種名（スコープ）を記載する。デジカメの場合Exifヘッダーの機種名とする。</t>
   </si>
   <si>
     <t>.participation[typeCode="DEV"].role.player.Entity[classCode="DEV"].name</t>
